--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty 200 Momentum 30 Index Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty 200 Momentum 30 Index Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="116">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty 200 Momentum 30 Index Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -79,34 +79,82 @@
     <t>Automobiles</t>
   </si>
   <si>
+    <t>Divi's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE361B01024</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals &amp; Biotechnology</t>
+  </si>
+  <si>
+    <t>Bharat Electronics Ltd.</t>
+  </si>
+  <si>
+    <t>INE263A01024</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense</t>
+  </si>
+  <si>
+    <t>BSE Ltd.</t>
+  </si>
+  <si>
+    <t>INE118H01025</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Tech Mahindra Ltd.</t>
+  </si>
+  <si>
+    <t>INE669C01036</t>
+  </si>
+  <si>
+    <t>It - Software</t>
+  </si>
+  <si>
+    <t>Sun Pharmaceutical Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE044A01036</t>
+  </si>
+  <si>
+    <t>Zomato Ltd.</t>
+  </si>
+  <si>
+    <t>INE758T01015</t>
+  </si>
+  <si>
+    <t>Retailing</t>
+  </si>
+  <si>
+    <t>HCL Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE860A01027</t>
+  </si>
+  <si>
     <t>Infosys Ltd.</t>
   </si>
   <si>
     <t>INE009A01021</t>
   </si>
   <si>
-    <t>It - Software</t>
-  </si>
-  <si>
-    <t>Tech Mahindra Ltd.</t>
-  </si>
-  <si>
-    <t>INE669C01036</t>
-  </si>
-  <si>
-    <t>Sun Pharmaceutical Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE044A01036</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals &amp; Biotechnology</t>
-  </si>
-  <si>
-    <t>HCL Technologies Ltd.</t>
-  </si>
-  <si>
-    <t>INE860A01027</t>
+    <t>Dixon Technologies (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE935N01020</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
+    <t>Trent Ltd.</t>
+  </si>
+  <si>
+    <t>INE849A01020</t>
   </si>
   <si>
     <t>Persistent Systems Ltd.</t>
@@ -115,45 +163,6 @@
     <t>INE262H01021</t>
   </si>
   <si>
-    <t>Divi's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE361B01024</t>
-  </si>
-  <si>
-    <t>Dixon Technologies (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE935N01020</t>
-  </si>
-  <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>Trent Ltd.</t>
-  </si>
-  <si>
-    <t>INE849A01020</t>
-  </si>
-  <si>
-    <t>Retailing</t>
-  </si>
-  <si>
-    <t>Zomato Ltd.</t>
-  </si>
-  <si>
-    <t>INE758T01015</t>
-  </si>
-  <si>
-    <t>Bharat Electronics Ltd.</t>
-  </si>
-  <si>
-    <t>INE263A01024</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
-  </si>
-  <si>
     <t>The Indian Hotels Company Ltd.</t>
   </si>
   <si>
@@ -163,34 +172,25 @@
     <t>Leisure Services</t>
   </si>
   <si>
+    <t>COFORGE Ltd.</t>
+  </si>
+  <si>
+    <t>INE591G01017</t>
+  </si>
+  <si>
+    <t>PB Fintech Ltd.</t>
+  </si>
+  <si>
+    <t>INE417T01026</t>
+  </si>
+  <si>
+    <t>Financial Technology (Fintech)</t>
+  </si>
+  <si>
     <t>Info Edge (India) Ltd.</t>
   </si>
   <si>
-    <t>INE663F01024</t>
-  </si>
-  <si>
-    <t>COFORGE Ltd.</t>
-  </si>
-  <si>
-    <t>INE591G01017</t>
-  </si>
-  <si>
-    <t>BSE Ltd.</t>
-  </si>
-  <si>
-    <t>INE118H01025</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>PB Fintech Ltd.</t>
-  </si>
-  <si>
-    <t>INE417T01026</t>
-  </si>
-  <si>
-    <t>Financial Technology (Fintech)</t>
+    <t>INE663F01032</t>
   </si>
   <si>
     <t>Vedanta Ltd.</t>
@@ -208,6 +208,63 @@
     <t>INE326A01037</t>
   </si>
   <si>
+    <t>United Spirits Ltd.</t>
+  </si>
+  <si>
+    <t>INE854D01024</t>
+  </si>
+  <si>
+    <t>Beverages</t>
+  </si>
+  <si>
+    <t>The Federal Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE171A01029</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
+    <t>Kalyan Jewellers India Ltd.</t>
+  </si>
+  <si>
+    <t>INE303R01014</t>
+  </si>
+  <si>
+    <t>Samvardhana Motherson International Ltd.</t>
+  </si>
+  <si>
+    <t>INE775A01035</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>Voltas Ltd.</t>
+  </si>
+  <si>
+    <t>INE226A01021</t>
+  </si>
+  <si>
+    <t>Torrent Pharmaceuticals Ltd.</t>
+  </si>
+  <si>
+    <t>INE685A01028</t>
+  </si>
+  <si>
+    <t>Oracle Financial Services Software Ltd.</t>
+  </si>
+  <si>
+    <t>INE881D01027</t>
+  </si>
+  <si>
+    <t>One 97 Communications Ltd</t>
+  </si>
+  <si>
+    <t>INE982J01020</t>
+  </si>
+  <si>
     <t>Siemens Ltd.</t>
   </si>
   <si>
@@ -217,63 +274,6 @@
     <t>Electrical Equipment</t>
   </si>
   <si>
-    <t>United Spirits Ltd.</t>
-  </si>
-  <si>
-    <t>INE854D01024</t>
-  </si>
-  <si>
-    <t>Beverages</t>
-  </si>
-  <si>
-    <t>The Federal Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE171A01029</t>
-  </si>
-  <si>
-    <t>Banks</t>
-  </si>
-  <si>
-    <t>Oracle Financial Services Software Ltd.</t>
-  </si>
-  <si>
-    <t>INE881D01027</t>
-  </si>
-  <si>
-    <t>Kalyan Jewellers India Ltd.</t>
-  </si>
-  <si>
-    <t>INE303R01014</t>
-  </si>
-  <si>
-    <t>Voltas Ltd.</t>
-  </si>
-  <si>
-    <t>INE226A01021</t>
-  </si>
-  <si>
-    <t>Samvardhana Motherson International Ltd.</t>
-  </si>
-  <si>
-    <t>INE775A01035</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>Torrent Pharmaceuticals Ltd.</t>
-  </si>
-  <si>
-    <t>INE685A01028</t>
-  </si>
-  <si>
-    <t>One 97 Communications Ltd</t>
-  </si>
-  <si>
-    <t>INE982J01020</t>
-  </si>
-  <si>
     <t>Bosch Ltd.</t>
   </si>
   <si>
@@ -289,6 +289,12 @@
     <t>Oil</t>
   </si>
   <si>
+    <t>SIEMENS ENERGY INDIA LTD</t>
+  </si>
+  <si>
+    <t>INE1NPP01017</t>
+  </si>
+  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -346,7 +352,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -356,9 +362,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - Nifty 200 Momentum 30 TRI</t>
   </si>
 </sst>
 </file>
@@ -729,13 +732,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -753,7 +756,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="15697200"/>
+          <a:off x="666750" y="15887700"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -768,13 +771,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>105</xdr:row>
+      <xdr:row>106</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -792,7 +795,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="18554700"/>
+          <a:off x="666750" y="18745200"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1226,10 +1229,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>46663.83999999999</v>
+        <v>55089.03</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9995227956949002</v>
+        <v>0.9990251028694999</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1263,10 +1266,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>46663.83999999999</v>
+        <v>55089.03</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9995227956949002</v>
+        <v>0.9990251028694999</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1289,13 +1292,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>160564</v>
+        <v>183642</v>
       </c>
       <c r="G8" s="15">
-        <v>2611.25</v>
+        <v>3408.76</v>
       </c>
       <c r="H8" s="16">
-        <v>0.0559320428893</v>
+        <v>0.0618169680907</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1318,13 +1321,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>86304</v>
+        <v>98708</v>
       </c>
       <c r="G9" s="15">
-        <v>2580.36</v>
+        <v>2938.34</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0552703901158</v>
+        <v>0.0532860248359</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1347,13 +1350,13 @@
         <v>23</v>
       </c>
       <c r="F10" s="14">
-        <v>134643</v>
+        <v>44247</v>
       </c>
       <c r="G10" s="15">
-        <v>2531.02</v>
+        <v>2925.61</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0542135449282</v>
+        <v>0.0530551696265</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1373,16 +1376,16 @@
         <v>13</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F11" s="14">
-        <v>149363</v>
+        <v>759199</v>
       </c>
       <c r="G11" s="15">
-        <v>2501.01</v>
+        <v>2919.88</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0535707414405</v>
+        <v>0.0529512575801</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1393,25 +1396,25 @@
     </row>
     <row r="12" spans="2:10" ht="15" customHeight="1">
       <c r="B12" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F12" s="14">
-        <v>139474</v>
+        <v>104253</v>
       </c>
       <c r="G12" s="15">
-        <v>2432.36</v>
+        <v>2787.73</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0521002829458</v>
+        <v>0.0505547520082</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1422,25 +1425,25 @@
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1">
       <c r="B13" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F13" s="14">
-        <v>135113</v>
+        <v>170828</v>
       </c>
       <c r="G13" s="15">
-        <v>2331.31</v>
+        <v>2688.66</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0499358280166</v>
+        <v>0.0487581435557</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1451,10 +1454,10 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>13</v>
@@ -1463,13 +1466,13 @@
         <v>23</v>
       </c>
       <c r="F14" s="14">
-        <v>35922</v>
+        <v>159517</v>
       </c>
       <c r="G14" s="15">
-        <v>2167.03</v>
+        <v>2676.06</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0464170090579</v>
+        <v>0.0485296458621</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1480,25 +1483,25 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F15" s="14">
-        <v>38687</v>
+        <v>1075205</v>
       </c>
       <c r="G15" s="15">
-        <v>2157.84</v>
+        <v>2562.32</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0462201625383</v>
+        <v>0.0464670008092</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1509,25 +1512,25 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F16" s="14">
-        <v>14229</v>
+        <v>154536</v>
       </c>
       <c r="G16" s="15">
-        <v>2132.35</v>
+        <v>2529.14</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0456741758372</v>
+        <v>0.0458652902161</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1538,25 +1541,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F17" s="14">
-        <v>36350</v>
+        <v>153992</v>
       </c>
       <c r="G17" s="15">
-        <v>2091.29</v>
+        <v>2406.43</v>
       </c>
       <c r="H17" s="16">
-        <v>0.044794685294</v>
+        <v>0.043639976567</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1567,25 +1570,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F18" s="14">
-        <v>940108</v>
+        <v>16275</v>
       </c>
       <c r="G18" s="15">
-        <v>2071.53</v>
+        <v>2391.12</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0443714331475</v>
+        <v>0.0433623337346</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1596,25 +1599,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F19" s="14">
-        <v>663811</v>
+        <v>41577</v>
       </c>
       <c r="G19" s="15">
-        <v>1942.64</v>
+        <v>2346.40</v>
       </c>
       <c r="H19" s="16">
-        <v>0.041610655356</v>
+        <v>0.0425513482698</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1625,25 +1628,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="F20" s="14">
-        <v>247776</v>
+        <v>41078</v>
       </c>
       <c r="G20" s="15">
-        <v>1894.74</v>
+        <v>2315.98</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0405846544544</v>
+        <v>0.0419996895524</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1663,16 +1666,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F21" s="14">
-        <v>21878</v>
+        <v>283383</v>
       </c>
       <c r="G21" s="15">
-        <v>1689.79</v>
+        <v>2181.62</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0361946986133</v>
+        <v>0.0395631062105</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1683,25 +1686,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F22" s="14">
-        <v>19678</v>
+        <v>22507</v>
       </c>
       <c r="G22" s="15">
-        <v>1626.16</v>
+        <v>1924.46</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0348317667266</v>
+        <v>0.0348995770931</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1712,25 +1715,25 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F23" s="14">
-        <v>30381</v>
+        <v>103089</v>
       </c>
       <c r="G23" s="15">
-        <v>1612</v>
+        <v>1816.02</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0345284645812</v>
+        <v>0.0329330461494</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1741,25 +1744,25 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F24" s="14">
-        <v>90137</v>
+        <v>125103</v>
       </c>
       <c r="G24" s="15">
-        <v>1556.49</v>
+        <v>1785.85</v>
       </c>
       <c r="H24" s="16">
-        <v>0.033339460196</v>
+        <v>0.0323859211164</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1782,13 +1785,13 @@
         <v>61</v>
       </c>
       <c r="F25" s="14">
-        <v>291127</v>
+        <v>332963</v>
       </c>
       <c r="G25" s="15">
-        <v>1285.03</v>
+        <v>1450.22</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0275248838962</v>
+        <v>0.0262993591407</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1808,16 +1811,16 @@
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F26" s="14">
-        <v>57688</v>
+        <v>65978</v>
       </c>
       <c r="G26" s="15">
-        <v>1200.17</v>
+        <v>1291.65</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0257072129878</v>
+        <v>0.0234237338018</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -1840,13 +1843,13 @@
         <v>66</v>
       </c>
       <c r="F27" s="14">
-        <v>18978</v>
+        <v>80890</v>
       </c>
       <c r="G27" s="15">
-        <v>1152.6</v>
+        <v>1229.61</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0246882805684</v>
+        <v>0.022298654682</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -1869,13 +1872,13 @@
         <v>69</v>
       </c>
       <c r="F28" s="14">
-        <v>70726</v>
+        <v>576471</v>
       </c>
       <c r="G28" s="15">
-        <v>1007.14</v>
+        <v>1164.82</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0215725792917</v>
+        <v>0.0211237050339</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -1895,16 +1898,16 @@
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="F29" s="14">
-        <v>504036</v>
+        <v>166428</v>
       </c>
       <c r="G29" s="15">
-        <v>943.61</v>
+        <v>932.66</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0202117893693</v>
+        <v>0.0169135443561</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -1915,25 +1918,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="D30" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>23</v>
-      </c>
       <c r="F30" s="14">
-        <v>8110</v>
+        <v>572256</v>
       </c>
       <c r="G30" s="15">
-        <v>739.80</v>
+        <v>876.24</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0158462519213</v>
+        <v>0.0158903824616</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -1953,16 +1956,16 @@
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F31" s="14">
-        <v>145517</v>
+        <v>64393</v>
       </c>
       <c r="G31" s="15">
-        <v>732.10</v>
+        <v>813.15</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0156813206699</v>
+        <v>0.0147462618673</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -1982,16 +1985,16 @@
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F32" s="14">
-        <v>56302</v>
+        <v>24710</v>
       </c>
       <c r="G32" s="15">
-        <v>709.88</v>
+        <v>784.47</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0152053762015</v>
+        <v>0.0142261575934</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2011,16 +2014,16 @@
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="F33" s="14">
-        <v>500354</v>
+        <v>9269</v>
       </c>
       <c r="G33" s="15">
-        <v>706.80</v>
+        <v>784.39</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0151394037009</v>
+        <v>0.0142247068144</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2031,25 +2034,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>83</v>
-      </c>
       <c r="D34" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="F34" s="14">
-        <v>21604</v>
+        <v>83018</v>
       </c>
       <c r="G34" s="15">
-        <v>706.26</v>
+        <v>739.23</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0151278370937</v>
+        <v>0.013405742065</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2060,25 +2063,25 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="D35" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="D35" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>58</v>
-      </c>
       <c r="F35" s="14">
-        <v>72586</v>
+        <v>21706</v>
       </c>
       <c r="G35" s="15">
-        <v>563.09</v>
+        <v>708.83</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0120611867996</v>
+        <v>0.0128544460424</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2098,16 +2101,16 @@
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F36" s="14">
-        <v>1797</v>
+        <v>2045</v>
       </c>
       <c r="G36" s="15">
-        <v>516.26</v>
+        <v>642.44</v>
       </c>
       <c r="H36" s="16">
-        <v>0.011058104916</v>
+        <v>0.0116504808142</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2130,13 +2133,13 @@
         <v>90</v>
       </c>
       <c r="F37" s="14">
-        <v>112245</v>
+        <v>128378</v>
       </c>
       <c r="G37" s="15">
-        <v>471.93</v>
+        <v>547.92</v>
       </c>
       <c r="H37" s="16">
-        <v>0.01010857214</v>
+        <v>0.0099363854176</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2147,6 +2150,27 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="F38" s="14">
+        <v>20944</v>
+      </c>
+      <c r="G38" s="15">
+        <v>519.02</v>
+      </c>
+      <c r="H38" s="16">
+        <v>0.0094122915014</v>
+      </c>
+      <c r="I38" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J38" s="11" t="s">
@@ -2154,28 +2178,7 @@
       </c>
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
-      <c r="B39" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I39" s="9" t="s">
+      <c r="B39" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J39" s="11" t="s">
@@ -2183,7 +2186,28 @@
       </c>
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I40" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J40" s="11" t="s">
@@ -2191,28 +2215,7 @@
       </c>
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
-      <c r="B41" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I41" s="9" t="s">
+      <c r="B41" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J41" s="11" t="s">
@@ -2220,7 +2223,28 @@
       </c>
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I42" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J42" s="11" t="s">
@@ -2228,36 +2252,36 @@
       </c>
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" ht="15" customHeight="1">
+      <c r="B44" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C43" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" ht="15" customHeight="1">
-      <c r="B44" s="12" t="s">
+      <c r="C44" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I44" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J44" s="11" t="s">
@@ -2265,36 +2289,36 @@
       </c>
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" ht="15" customHeight="1">
+      <c r="B46" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C45" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" ht="15" customHeight="1">
-      <c r="B46" s="12" t="s">
+      <c r="H46" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I46" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J46" s="11" t="s">
@@ -2302,28 +2326,7 @@
       </c>
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
-      <c r="B47" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I47" s="9" t="s">
+      <c r="B47" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J47" s="11" t="s">
@@ -2331,7 +2334,28 @@
       </c>
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I48" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J48" s="11" t="s">
@@ -2339,28 +2363,7 @@
       </c>
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
-      <c r="B49" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I49" s="9" t="s">
+      <c r="B49" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J49" s="11" t="s">
@@ -2368,7 +2371,28 @@
       </c>
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I50" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J50" s="11" t="s">
@@ -2376,28 +2400,7 @@
       </c>
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
-      <c r="B51" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I51" s="9" t="s">
+      <c r="B51" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J51" s="11" t="s">
@@ -2405,7 +2408,28 @@
       </c>
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I52" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J52" s="11" t="s">
@@ -2413,28 +2437,7 @@
       </c>
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
-      <c r="B53" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I53" s="9" t="s">
+      <c r="B53" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J53" s="11" t="s">
@@ -2442,7 +2445,28 @@
       </c>
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
-      <c r="B54" s="12" t="s">
+      <c r="B54" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I54" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J54" s="11" t="s">
@@ -2450,28 +2474,7 @@
       </c>
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
-      <c r="B55" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I55" s="9" t="s">
+      <c r="B55" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J55" s="11" t="s">
@@ -2479,7 +2482,28 @@
       </c>
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H56" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I56" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J56" s="11" t="s">
@@ -2487,28 +2511,7 @@
       </c>
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
-      <c r="B57" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I57" s="9" t="s">
+      <c r="B57" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J57" s="11" t="s">
@@ -2516,7 +2519,28 @@
       </c>
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I58" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J58" s="11" t="s">
@@ -2524,28 +2548,7 @@
       </c>
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
-      <c r="B59" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I59" s="9" t="s">
+      <c r="B59" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J59" s="11" t="s">
@@ -2553,7 +2556,28 @@
       </c>
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H60" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I60" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J60" s="11" t="s">
@@ -2561,28 +2585,7 @@
       </c>
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
-      <c r="B61" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I61" s="9" t="s">
+      <c r="B61" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J61" s="11" t="s">
@@ -2590,7 +2593,28 @@
       </c>
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
-      <c r="B62" s="12" t="s">
+      <c r="B62" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H62" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I62" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J62" s="11" t="s">
@@ -2598,28 +2622,7 @@
       </c>
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
-      <c r="B63" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D63" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I63" s="9" t="s">
+      <c r="B63" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J63" s="11" t="s">
@@ -2627,7 +2630,28 @@
       </c>
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H64" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I64" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J64" s="11" t="s">
@@ -2635,28 +2659,7 @@
       </c>
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
-      <c r="B65" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G65" s="9">
-        <v>487.53</v>
-      </c>
-      <c r="H65" s="10">
-        <v>0.0104427185715</v>
-      </c>
-      <c r="I65" s="9" t="s">
+      <c r="B65" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J65" s="11" t="s">
@@ -2664,7 +2667,28 @@
       </c>
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
-      <c r="B66" s="12" t="s">
+      <c r="B66" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="9">
+        <v>119.50</v>
+      </c>
+      <c r="H66" s="10">
+        <v>0.0021671011414</v>
+      </c>
+      <c r="I66" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J66" s="11" t="s">
@@ -2672,37 +2696,16 @@
       </c>
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
-      <c r="B67" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C67" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D67" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G67" s="18">
-        <v>-465.2511831899974</v>
-      </c>
-      <c r="H67" s="19">
-        <v>-0.009965514268075699</v>
-      </c>
-      <c r="I67" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J67" s="20" t="s">
+      <c r="B67" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C68" s="18" t="s">
         <v>13</v>
@@ -2717,10 +2720,10 @@
         <v>13</v>
       </c>
       <c r="G68" s="18">
-        <v>46686.11881681</v>
+        <v>-65.74145377000968</v>
       </c>
       <c r="H68" s="19">
-        <v>0.9999999999983242</v>
+        <v>-0.001192204012586235</v>
       </c>
       <c r="I68" s="18" t="s">
         <v>13</v>
@@ -2729,21 +2732,38 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="2:9" ht="15" customHeight="1">
-      <c r="B71" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="21"/>
-    </row>
-    <row r="72" spans="2:8" ht="15" customHeight="1">
+    <row r="69" spans="2:10" ht="15" customHeight="1">
+      <c r="B69" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="18">
+        <v>55142.78854623</v>
+      </c>
+      <c r="H69" s="19">
+        <v>0.9999999999983138</v>
+      </c>
+      <c r="I69" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J69" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" ht="15" customHeight="1">
       <c r="B72" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C72" s="21"/>
       <c r="D72" s="21"/>
@@ -2751,10 +2771,11 @@
       <c r="F72" s="21"/>
       <c r="G72" s="21"/>
       <c r="H72" s="21"/>
-    </row>
-    <row r="73" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B73" s="22" t="s">
-        <v>109</v>
+      <c r="I72" s="21"/>
+    </row>
+    <row r="73" spans="2:8" ht="15" customHeight="1">
+      <c r="B73" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="C73" s="21"/>
       <c r="D73" s="21"/>
@@ -2765,7 +2786,7 @@
     </row>
     <row r="74" spans="2:8" ht="27.6" customHeight="1">
       <c r="B74" s="22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C74" s="21"/>
       <c r="D74" s="21"/>
@@ -2776,7 +2797,7 @@
     </row>
     <row r="75" spans="2:8" ht="27.6" customHeight="1">
       <c r="B75" s="22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C75" s="21"/>
       <c r="D75" s="21"/>
@@ -2785,31 +2806,37 @@
       <c r="G75" s="21"/>
       <c r="H75" s="21"/>
     </row>
-    <row r="78" ht="15">
-      <c r="B78" s="21" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="93" ht="15">
-      <c r="B93" s="21" t="s">
+    <row r="76" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B76" s="22" t="s">
         <v>113</v>
+      </c>
+      <c r="C76" s="21"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="21"/>
+      <c r="F76" s="21"/>
+      <c r="G76" s="21"/>
+      <c r="H76" s="21"/>
+    </row>
+    <row r="79" ht="15">
+      <c r="B79" s="21" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="94" ht="15">
       <c r="B94" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B73:H73"/>
     <mergeCell ref="B74:H74"/>
     <mergeCell ref="B75:H75"/>
+    <mergeCell ref="B76:H76"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B71:I71"/>
-    <mergeCell ref="B72:H72"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B73:H73"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
